--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608383</v>
+        <v>122608835</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556258</v>
+        <v>556298</v>
       </c>
       <c r="R2" t="n">
-        <v>7071746</v>
+        <v>7071866</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608564</v>
+        <v>122608533</v>
       </c>
       <c r="B3" t="n">
-        <v>82443</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556321</v>
+        <v>556317</v>
       </c>
       <c r="R3" t="n">
-        <v>7071747</v>
+        <v>7071749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608835</v>
+        <v>122608719</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,27 +925,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556298</v>
+        <v>556316</v>
       </c>
       <c r="R4" t="n">
-        <v>7071866</v>
+        <v>7071796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608719</v>
+        <v>122608960</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,31 +1046,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556316</v>
+        <v>556264</v>
       </c>
       <c r="R5" t="n">
-        <v>7071796</v>
+        <v>7071895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608708</v>
+        <v>122608888</v>
       </c>
       <c r="B6" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556315</v>
+        <v>556257</v>
       </c>
       <c r="R6" t="n">
-        <v>7071799</v>
+        <v>7071876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608149</v>
+        <v>122608564</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,39 +1285,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556264</v>
+        <v>556321</v>
       </c>
       <c r="R7" t="n">
-        <v>7071834</v>
+        <v>7071747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608960</v>
+        <v>122608325</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>55983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,21 +1397,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,14 +1422,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556264</v>
+        <v>556259</v>
       </c>
       <c r="R8" t="n">
-        <v>7071895</v>
+        <v>7071767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608325</v>
+        <v>122608149</v>
       </c>
       <c r="B9" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,39 +1514,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556259</v>
+        <v>556264</v>
       </c>
       <c r="R9" t="n">
-        <v>7071767</v>
+        <v>7071834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608533</v>
+        <v>122608708</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,21 +1636,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1650,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556317</v>
+        <v>556315</v>
       </c>
       <c r="R10" t="n">
-        <v>7071749</v>
+        <v>7071799</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608888</v>
+        <v>122608383</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,39 +1748,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556257</v>
+        <v>556258</v>
       </c>
       <c r="R11" t="n">
-        <v>7071876</v>
+        <v>7071746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,12 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,12 +1832,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608533</v>
+        <v>122608960</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556317</v>
+        <v>556264</v>
       </c>
       <c r="R3" t="n">
-        <v>7071749</v>
+        <v>7071895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608719</v>
+        <v>122608325</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>55983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,43 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556316</v>
+        <v>556259</v>
       </c>
       <c r="R4" t="n">
-        <v>7071796</v>
+        <v>7071767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608960</v>
+        <v>122608533</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556264</v>
+        <v>556317</v>
       </c>
       <c r="R5" t="n">
-        <v>7071895</v>
+        <v>7071749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608888</v>
+        <v>122608564</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556257</v>
+        <v>556321</v>
       </c>
       <c r="R6" t="n">
-        <v>7071876</v>
+        <v>7071747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608564</v>
+        <v>122608383</v>
       </c>
       <c r="B7" t="n">
-        <v>82443</v>
+        <v>90851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,34 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556321</v>
+        <v>556258</v>
       </c>
       <c r="R7" t="n">
-        <v>7071747</v>
+        <v>7071746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608325</v>
+        <v>122608149</v>
       </c>
       <c r="B8" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,39 +1383,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556259</v>
+        <v>556264</v>
       </c>
       <c r="R8" t="n">
-        <v>7071767</v>
+        <v>7071834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608149</v>
+        <v>122608888</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1534,7 +1525,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1543,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556264</v>
+        <v>556257</v>
       </c>
       <c r="R9" t="n">
-        <v>7071834</v>
+        <v>7071876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1608,22 +1599,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608708</v>
+        <v>122608719</v>
       </c>
       <c r="B10" t="n">
-        <v>90857</v>
+        <v>57536</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,34 +1627,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556315</v>
+        <v>556316</v>
       </c>
       <c r="R10" t="n">
-        <v>7071799</v>
+        <v>7071796</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608383</v>
+        <v>122608708</v>
       </c>
       <c r="B11" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,14 +1768,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556258</v>
+        <v>556315</v>
       </c>
       <c r="R11" t="n">
-        <v>7071746</v>
+        <v>7071799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608835</v>
+        <v>122608564</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>82443</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556298</v>
+        <v>556321</v>
       </c>
       <c r="R2" t="n">
-        <v>7071866</v>
+        <v>7071747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608960</v>
+        <v>122608383</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>90851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556264</v>
+        <v>556258</v>
       </c>
       <c r="R3" t="n">
-        <v>7071895</v>
+        <v>7071746</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608325</v>
+        <v>122608149</v>
       </c>
       <c r="B4" t="n">
-        <v>55983</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556259</v>
+        <v>556264</v>
       </c>
       <c r="R4" t="n">
-        <v>7071767</v>
+        <v>7071834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608533</v>
+        <v>122608888</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556317</v>
+        <v>556257</v>
       </c>
       <c r="R5" t="n">
-        <v>7071749</v>
+        <v>7071876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608564</v>
+        <v>122608533</v>
       </c>
       <c r="B6" t="n">
-        <v>82443</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556321</v>
+        <v>556317</v>
       </c>
       <c r="R6" t="n">
-        <v>7071747</v>
+        <v>7071749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608383</v>
+        <v>122608719</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>57536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1271,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556258</v>
+        <v>556316</v>
       </c>
       <c r="R7" t="n">
-        <v>7071746</v>
+        <v>7071796</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1376,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608149</v>
+        <v>122608835</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1412,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556264</v>
+        <v>556298</v>
       </c>
       <c r="R8" t="n">
-        <v>7071834</v>
+        <v>7071866</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608888</v>
+        <v>122608960</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,16 +1514,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1534,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556257</v>
+        <v>556264</v>
       </c>
       <c r="R9" t="n">
-        <v>7071876</v>
+        <v>7071895</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608719</v>
+        <v>122608325</v>
       </c>
       <c r="B10" t="n">
-        <v>57536</v>
+        <v>55983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,43 +1631,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556316</v>
+        <v>556259</v>
       </c>
       <c r="R10" t="n">
-        <v>7071796</v>
+        <v>7071767</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608564</v>
+        <v>122608383</v>
       </c>
       <c r="B2" t="n">
-        <v>82443</v>
+        <v>90852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556321</v>
+        <v>556258</v>
       </c>
       <c r="R2" t="n">
-        <v>7071747</v>
+        <v>7071746</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608383</v>
+        <v>122608564</v>
       </c>
       <c r="B3" t="n">
-        <v>90851</v>
+        <v>82444</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556258</v>
+        <v>556321</v>
       </c>
       <c r="R3" t="n">
-        <v>7071746</v>
+        <v>7071747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608149</v>
+        <v>122608960</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,7 +947,7 @@
         <v>556264</v>
       </c>
       <c r="R4" t="n">
-        <v>7071834</v>
+        <v>7071895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608888</v>
+        <v>122608708</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556257</v>
+        <v>556315</v>
       </c>
       <c r="R5" t="n">
-        <v>7071876</v>
+        <v>7071799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608533</v>
+        <v>122608719</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1144,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556317</v>
+        <v>556316</v>
       </c>
       <c r="R6" t="n">
-        <v>7071749</v>
+        <v>7071796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608719</v>
+        <v>122608149</v>
       </c>
       <c r="B7" t="n">
-        <v>57536</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,31 +1265,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556316</v>
+        <v>556264</v>
       </c>
       <c r="R7" t="n">
-        <v>7071796</v>
+        <v>7071834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1339,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608835</v>
+        <v>122608888</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,7 +1407,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556298</v>
+        <v>556257</v>
       </c>
       <c r="R8" t="n">
-        <v>7071866</v>
+        <v>7071876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1481,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608960</v>
+        <v>122608533</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,39 +1509,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556264</v>
+        <v>556317</v>
       </c>
       <c r="R9" t="n">
-        <v>7071895</v>
+        <v>7071749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,22 +1593,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608325</v>
+        <v>122608835</v>
       </c>
       <c r="B10" t="n">
-        <v>55983</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,39 +1621,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556259</v>
+        <v>556298</v>
       </c>
       <c r="R10" t="n">
-        <v>7071767</v>
+        <v>7071866</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1695,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608708</v>
+        <v>122608325</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>55984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,34 +1743,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556315</v>
+        <v>556259</v>
       </c>
       <c r="R11" t="n">
-        <v>7071799</v>
+        <v>7071767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608383</v>
+        <v>122608533</v>
       </c>
       <c r="B2" t="n">
-        <v>90852</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556258</v>
+        <v>556317</v>
       </c>
       <c r="R2" t="n">
-        <v>7071746</v>
+        <v>7071749</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608564</v>
+        <v>122608383</v>
       </c>
       <c r="B3" t="n">
-        <v>82444</v>
+        <v>90855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556321</v>
+        <v>556258</v>
       </c>
       <c r="R3" t="n">
-        <v>7071747</v>
+        <v>7071746</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608960</v>
+        <v>122608888</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556264</v>
+        <v>556257</v>
       </c>
       <c r="R4" t="n">
-        <v>7071895</v>
+        <v>7071876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608708</v>
+        <v>122608719</v>
       </c>
       <c r="B5" t="n">
-        <v>90852</v>
+        <v>57537</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1037,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556315</v>
+        <v>556316</v>
       </c>
       <c r="R5" t="n">
-        <v>7071799</v>
+        <v>7071796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608719</v>
+        <v>122608835</v>
       </c>
       <c r="B6" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,31 +1158,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556316</v>
+        <v>556298</v>
       </c>
       <c r="R6" t="n">
-        <v>7071796</v>
+        <v>7071866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608149</v>
+        <v>122608708</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1280,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556264</v>
+        <v>556315</v>
       </c>
       <c r="R7" t="n">
-        <v>7071834</v>
+        <v>7071799</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608888</v>
+        <v>122608564</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>82447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,39 +1392,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556257</v>
+        <v>556321</v>
       </c>
       <c r="R8" t="n">
-        <v>7071876</v>
+        <v>7071747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,22 +1476,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608533</v>
+        <v>122608960</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,34 +1504,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556317</v>
+        <v>556264</v>
       </c>
       <c r="R9" t="n">
-        <v>7071749</v>
+        <v>7071895</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,19 +1593,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608835</v>
+        <v>122608149</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556298</v>
+        <v>556264</v>
       </c>
       <c r="R10" t="n">
-        <v>7071866</v>
+        <v>7071834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608533</v>
+        <v>122608325</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>55984</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556317</v>
+        <v>556259</v>
       </c>
       <c r="R2" t="n">
-        <v>7071749</v>
+        <v>7071767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608383</v>
+        <v>122608835</v>
       </c>
       <c r="B3" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556258</v>
+        <v>556298</v>
       </c>
       <c r="R3" t="n">
-        <v>7071746</v>
+        <v>7071866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608888</v>
+        <v>122608960</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,16 +930,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -944,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556257</v>
+        <v>556264</v>
       </c>
       <c r="R4" t="n">
-        <v>7071876</v>
+        <v>7071895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608719</v>
+        <v>122608149</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,31 +1047,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556316</v>
+        <v>556264</v>
       </c>
       <c r="R5" t="n">
-        <v>7071796</v>
+        <v>7071834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608835</v>
+        <v>122608383</v>
       </c>
       <c r="B6" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,39 +1169,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556298</v>
+        <v>556258</v>
       </c>
       <c r="R6" t="n">
-        <v>7071866</v>
+        <v>7071746</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608708</v>
+        <v>122608533</v>
       </c>
       <c r="B7" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556315</v>
+        <v>556317</v>
       </c>
       <c r="R7" t="n">
-        <v>7071799</v>
+        <v>7071749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608564</v>
+        <v>122608708</v>
       </c>
       <c r="B8" t="n">
-        <v>82447</v>
+        <v>90855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556321</v>
+        <v>556315</v>
       </c>
       <c r="R8" t="n">
-        <v>7071747</v>
+        <v>7071799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608960</v>
+        <v>122608719</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,27 +1505,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556264</v>
+        <v>556316</v>
       </c>
       <c r="R9" t="n">
-        <v>7071895</v>
+        <v>7071796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,22 +1598,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608149</v>
+        <v>122608564</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>82447</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,39 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556264</v>
+        <v>556321</v>
       </c>
       <c r="R10" t="n">
-        <v>7071834</v>
+        <v>7071747</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,12 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608325</v>
+        <v>122608888</v>
       </c>
       <c r="B11" t="n">
-        <v>55984</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,21 +1738,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,14 +1763,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556259</v>
+        <v>556257</v>
       </c>
       <c r="R11" t="n">
-        <v>7071767</v>
+        <v>7071876</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1812,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,12 +1832,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608719</v>
+        <v>122608564</v>
       </c>
       <c r="B9" t="n">
-        <v>57537</v>
+        <v>82447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,43 +1505,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556316</v>
+        <v>556321</v>
       </c>
       <c r="R9" t="n">
-        <v>7071796</v>
+        <v>7071747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608564</v>
+        <v>122608888</v>
       </c>
       <c r="B10" t="n">
-        <v>82447</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1617,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556321</v>
+        <v>556257</v>
       </c>
       <c r="R10" t="n">
-        <v>7071747</v>
+        <v>7071876</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1691,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,22 +1711,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608888</v>
+        <v>122608719</v>
       </c>
       <c r="B11" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,27 +1739,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556257</v>
+        <v>556316</v>
       </c>
       <c r="R11" t="n">
-        <v>7071876</v>
+        <v>7071796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,12 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,12 +1832,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608564</v>
+        <v>122608383</v>
       </c>
       <c r="B2" t="n">
-        <v>82549</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556321</v>
+        <v>556258</v>
       </c>
       <c r="R2" t="n">
-        <v>7071747</v>
+        <v>7071746</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608888</v>
+        <v>122608960</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556257</v>
+        <v>556264</v>
       </c>
       <c r="R3" t="n">
-        <v>7071876</v>
+        <v>7071895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608325</v>
+        <v>122608564</v>
       </c>
       <c r="B4" t="n">
-        <v>56078</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556259</v>
+        <v>556321</v>
       </c>
       <c r="R4" t="n">
-        <v>7071767</v>
+        <v>7071747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608835</v>
+        <v>122608325</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>56078</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,39 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556298</v>
+        <v>556259</v>
       </c>
       <c r="R5" t="n">
-        <v>7071866</v>
+        <v>7071767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608960</v>
+        <v>122608708</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556264</v>
+        <v>556315</v>
       </c>
       <c r="R6" t="n">
-        <v>7071895</v>
+        <v>7071799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608708</v>
+        <v>122608533</v>
       </c>
       <c r="B7" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556315</v>
+        <v>556317</v>
       </c>
       <c r="R7" t="n">
-        <v>7071799</v>
+        <v>7071749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608719</v>
+        <v>122608888</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,31 +1373,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556316</v>
+        <v>556257</v>
       </c>
       <c r="R8" t="n">
-        <v>7071796</v>
+        <v>7071876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608383</v>
+        <v>122608719</v>
       </c>
       <c r="B9" t="n">
-        <v>90958</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,34 +1495,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556258</v>
+        <v>556316</v>
       </c>
       <c r="R9" t="n">
-        <v>7071746</v>
+        <v>7071796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608533</v>
+        <v>122608149</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1616,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556317</v>
+        <v>556264</v>
       </c>
       <c r="R10" t="n">
-        <v>7071749</v>
+        <v>7071834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1690,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608149</v>
+        <v>122608835</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556264</v>
+        <v>556298</v>
       </c>
       <c r="R11" t="n">
-        <v>7071834</v>
+        <v>7071866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608383</v>
+        <v>122608888</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556258</v>
+        <v>556257</v>
       </c>
       <c r="R2" t="n">
-        <v>7071746</v>
+        <v>7071876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +785,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -904,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608564</v>
+        <v>122608719</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +930,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556321</v>
+        <v>556316</v>
       </c>
       <c r="R4" t="n">
-        <v>7071747</v>
+        <v>7071796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608325</v>
+        <v>122608708</v>
       </c>
       <c r="B5" t="n">
-        <v>56078</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1051,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556259</v>
+        <v>556315</v>
       </c>
       <c r="R5" t="n">
-        <v>7071767</v>
+        <v>7071799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608708</v>
+        <v>122608149</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556315</v>
+        <v>556264</v>
       </c>
       <c r="R6" t="n">
-        <v>7071799</v>
+        <v>7071834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608533</v>
+        <v>122608564</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1285,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556317</v>
+        <v>556321</v>
       </c>
       <c r="R7" t="n">
-        <v>7071749</v>
+        <v>7071747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608888</v>
+        <v>122608835</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1393,7 +1417,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556257</v>
+        <v>556298</v>
       </c>
       <c r="R8" t="n">
-        <v>7071876</v>
+        <v>7071866</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1491,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608719</v>
+        <v>122608533</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,43 +1519,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556316</v>
+        <v>556317</v>
       </c>
       <c r="R9" t="n">
-        <v>7071796</v>
+        <v>7071749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608149</v>
+        <v>122608383</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1631,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556264</v>
+        <v>556258</v>
       </c>
       <c r="R10" t="n">
-        <v>7071834</v>
+        <v>7071746</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,12 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608835</v>
+        <v>122608325</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>56078</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,39 +1743,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556298</v>
+        <v>556259</v>
       </c>
       <c r="R11" t="n">
-        <v>7071866</v>
+        <v>7071767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,12 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608888</v>
+        <v>122608960</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556257</v>
+        <v>556264</v>
       </c>
       <c r="R2" t="n">
-        <v>7071876</v>
+        <v>7071895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608960</v>
+        <v>122608888</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556264</v>
+        <v>556257</v>
       </c>
       <c r="R3" t="n">
-        <v>7071895</v>
+        <v>7071876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608719</v>
+        <v>122608325</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>56078</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,43 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556316</v>
+        <v>556259</v>
       </c>
       <c r="R4" t="n">
-        <v>7071796</v>
+        <v>7071767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608708</v>
+        <v>122608719</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,34 +1047,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556315</v>
+        <v>556316</v>
       </c>
       <c r="R5" t="n">
-        <v>7071799</v>
+        <v>7071796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608149</v>
+        <v>122608533</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1168,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556264</v>
+        <v>556317</v>
       </c>
       <c r="R6" t="n">
-        <v>7071834</v>
+        <v>7071749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608564</v>
+        <v>122608149</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,34 +1280,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556321</v>
+        <v>556264</v>
       </c>
       <c r="R7" t="n">
-        <v>7071747</v>
+        <v>7071834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608835</v>
+        <v>122608564</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,39 +1402,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556298</v>
+        <v>556321</v>
       </c>
       <c r="R8" t="n">
-        <v>7071866</v>
+        <v>7071747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608533</v>
+        <v>122608835</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,34 +1514,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556317</v>
+        <v>556298</v>
       </c>
       <c r="R9" t="n">
-        <v>7071749</v>
+        <v>7071866</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,7 +1620,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608383</v>
+        <v>122608708</v>
       </c>
       <c r="B10" t="n">
         <v>90962</v>
@@ -1651,14 +1656,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556258</v>
+        <v>556315</v>
       </c>
       <c r="R10" t="n">
-        <v>7071746</v>
+        <v>7071799</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608325</v>
+        <v>122608383</v>
       </c>
       <c r="B11" t="n">
-        <v>56078</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,39 +1748,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556259</v>
+        <v>556258</v>
       </c>
       <c r="R11" t="n">
-        <v>7071767</v>
+        <v>7071746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608960</v>
+        <v>122608708</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556264</v>
+        <v>556315</v>
       </c>
       <c r="R2" t="n">
-        <v>7071895</v>
+        <v>7071799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608888</v>
+        <v>122608533</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556257</v>
+        <v>556317</v>
       </c>
       <c r="R3" t="n">
-        <v>7071876</v>
+        <v>7071749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1031,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608719</v>
+        <v>122608564</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>82553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,43 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556316</v>
+        <v>556321</v>
       </c>
       <c r="R5" t="n">
-        <v>7071796</v>
+        <v>7071747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608533</v>
+        <v>122608383</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,34 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556317</v>
+        <v>556258</v>
       </c>
       <c r="R6" t="n">
-        <v>7071749</v>
+        <v>7071746</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608149</v>
+        <v>122608960</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,16 +1256,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1300,7 +1276,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1312,7 +1288,7 @@
         <v>556264</v>
       </c>
       <c r="R7" t="n">
-        <v>7071834</v>
+        <v>7071895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608564</v>
+        <v>122608719</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,34 +1373,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556321</v>
+        <v>556316</v>
       </c>
       <c r="R8" t="n">
-        <v>7071747</v>
+        <v>7071796</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608835</v>
+        <v>122608888</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1534,7 +1514,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1543,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556298</v>
+        <v>556257</v>
       </c>
       <c r="R9" t="n">
-        <v>7071866</v>
+        <v>7071876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1568,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,22 +1588,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608708</v>
+        <v>122608835</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,34 +1616,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556315</v>
+        <v>556298</v>
       </c>
       <c r="R10" t="n">
-        <v>7071799</v>
+        <v>7071866</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1690,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608383</v>
+        <v>122608149</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,34 +1738,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556258</v>
+        <v>556264</v>
       </c>
       <c r="R11" t="n">
-        <v>7071746</v>
+        <v>7071834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1812,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608708</v>
+        <v>122608149</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556315</v>
+        <v>556264</v>
       </c>
       <c r="R2" t="n">
-        <v>7071799</v>
+        <v>7071834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608533</v>
+        <v>122608383</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556317</v>
+        <v>556258</v>
       </c>
       <c r="R3" t="n">
-        <v>7071749</v>
+        <v>7071746</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608325</v>
+        <v>122608960</v>
       </c>
       <c r="B4" t="n">
-        <v>56078</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,14 +950,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556259</v>
+        <v>556264</v>
       </c>
       <c r="R4" t="n">
-        <v>7071767</v>
+        <v>7071895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608564</v>
+        <v>122608533</v>
       </c>
       <c r="B5" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556321</v>
+        <v>556317</v>
       </c>
       <c r="R5" t="n">
-        <v>7071747</v>
+        <v>7071749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608383</v>
+        <v>122608719</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1154,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556258</v>
+        <v>556316</v>
       </c>
       <c r="R6" t="n">
-        <v>7071746</v>
+        <v>7071796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608960</v>
+        <v>122608888</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,16 +1275,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1285,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556264</v>
+        <v>556257</v>
       </c>
       <c r="R7" t="n">
-        <v>7071895</v>
+        <v>7071876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608719</v>
+        <v>122608325</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>56078</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,43 +1397,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556316</v>
+        <v>556259</v>
       </c>
       <c r="R8" t="n">
-        <v>7071796</v>
+        <v>7071767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608888</v>
+        <v>122608564</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,39 +1514,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556257</v>
+        <v>556321</v>
       </c>
       <c r="R9" t="n">
-        <v>7071876</v>
+        <v>7071747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,12 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,22 +1598,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608835</v>
+        <v>122608708</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556298</v>
+        <v>556315</v>
       </c>
       <c r="R10" t="n">
-        <v>7071866</v>
+        <v>7071799</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,12 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608149</v>
+        <v>122608835</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556264</v>
+        <v>556298</v>
       </c>
       <c r="R11" t="n">
-        <v>7071834</v>
+        <v>7071866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 58336-2024 artfynd.xlsx
+++ b/artfynd/A 58336-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122608149</v>
+        <v>122608383</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556264</v>
+        <v>556258</v>
       </c>
       <c r="R2" t="n">
-        <v>7071834</v>
+        <v>7071746</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122608383</v>
+        <v>122608149</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556258</v>
+        <v>556264</v>
       </c>
       <c r="R3" t="n">
-        <v>7071746</v>
+        <v>7071834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122608960</v>
+        <v>122608325</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>56078</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,14 +950,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästflomyran, Hästflomyran, Ång</t>
+          <t>Bjurbäcken, Bjurbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556264</v>
+        <v>556259</v>
       </c>
       <c r="R4" t="n">
-        <v>7071895</v>
+        <v>7071767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122608533</v>
+        <v>122608708</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556317</v>
+        <v>556315</v>
       </c>
       <c r="R5" t="n">
-        <v>7071749</v>
+        <v>7071799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122608719</v>
+        <v>122608960</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,31 +1154,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1187,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556316</v>
+        <v>556264</v>
       </c>
       <c r="R6" t="n">
-        <v>7071796</v>
+        <v>7071895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,19 +1243,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122608888</v>
+        <v>122608835</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1295,7 +1291,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556257</v>
+        <v>556298</v>
       </c>
       <c r="R7" t="n">
-        <v>7071876</v>
+        <v>7071866</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,22 +1365,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122608325</v>
+        <v>122608888</v>
       </c>
       <c r="B8" t="n">
-        <v>56078</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,14 +1418,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjurbäcken, Bjurbäcken, Ång</t>
+          <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556259</v>
+        <v>556257</v>
       </c>
       <c r="R8" t="n">
-        <v>7071767</v>
+        <v>7071876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1487,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122608564</v>
+        <v>122608719</v>
       </c>
       <c r="B9" t="n">
-        <v>82553</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,34 +1515,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556321</v>
+        <v>556316</v>
       </c>
       <c r="R9" t="n">
-        <v>7071747</v>
+        <v>7071796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122608708</v>
+        <v>122608564</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,21 +1636,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1650,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556315</v>
+        <v>556321</v>
       </c>
       <c r="R10" t="n">
-        <v>7071799</v>
+        <v>7071747</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122608835</v>
+        <v>122608533</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,39 +1748,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hästflomyran, Hästflomyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556298</v>
+        <v>556317</v>
       </c>
       <c r="R11" t="n">
-        <v>7071866</v>
+        <v>7071749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,12 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
